--- a/community-events.xlsx
+++ b/community-events.xlsx
@@ -468,7 +468,7 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">                Videos: an .mp4/.webm/.mov file, OR a YouTube / Vimeo link (shown as an embedded player).</t>
+          <t xml:space="preserve">                Videos: an .mp4/.webm/.mov file, OR a YouTube, Vimeo or Wistia link (shown as an embedded player).</t>
         </is>
       </c>
     </row>
